--- a/customboard/droneboard/bom.xlsx
+++ b/customboard/droneboard/bom.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="83">
   <si>
     <t xml:space="preserve">xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -206,24 +206,39 @@
     <t xml:space="preserve">D1</t>
   </si>
   <si>
+    <t xml:space="preserve">Foshan NationStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCD0603Y5</t>
+  </si>
+  <si>
     <t xml:space="preserve">LED SMD Yellow 2V 20ma 0603</t>
   </si>
   <si>
     <t xml:space="preserve">D2</t>
   </si>
   <si>
+    <t xml:space="preserve">NCD0603R1</t>
+  </si>
+  <si>
     <t xml:space="preserve">LED SMD Red 2V 20ma 0603</t>
   </si>
   <si>
     <t xml:space="preserve">D3</t>
   </si>
   <si>
+    <t xml:space="preserve">NCD0603G3</t>
+  </si>
+  <si>
     <t xml:space="preserve">LED SMD Green 2V 20ma 0603</t>
   </si>
   <si>
     <t xml:space="preserve">D4</t>
   </si>
   <si>
+    <t xml:space="preserve">NCD0603B5</t>
+  </si>
+  <si>
     <t xml:space="preserve">LED SMD Blue 2V 20ma 0603</t>
   </si>
   <si>
@@ -236,7 +251,7 @@
     <t xml:space="preserve">R7</t>
   </si>
   <si>
-    <t xml:space="preserve">RES 10K OHM 0.1W 1% 0603 SMD</t>
+    <t xml:space="preserve">RES 10K OHM 0.1W 0.1% 0603 SMD</t>
   </si>
   <si>
     <t xml:space="preserve">R3, R4, R5, R6</t>
@@ -248,7 +263,7 @@
     <t xml:space="preserve">R8</t>
   </si>
   <si>
-    <t xml:space="preserve">RES 1K OHM 0.1W 1% 0603 SMD</t>
+    <t xml:space="preserve">RES 1K OHM 0.1W 0.1% 0603 SMD</t>
   </si>
   <si>
     <t xml:space="preserve">U1</t>
@@ -318,6 +333,18 @@
   </si>
   <si>
     <t xml:space="preserve">3-SMD, Non-Standard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47346-0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB Connectors MICRO USB B RECPT BTTM MOUNT </t>
   </si>
   <si>
     <t xml:space="preserve">Need a quick and accurante quote? Need an efficient production? Please read SMT Ordering Necessary Files &amp; Info in 1 minute. Thank you very much!</t>
@@ -400,9 +427,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -563,11 +591,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -687,9 +715,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>665640</xdr:colOff>
+      <xdr:colOff>665280</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>155880</xdr:rowOff>
+      <xdr:rowOff>155520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -703,7 +731,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9360" y="203760"/>
-          <a:ext cx="1376280" cy="375120"/>
+          <a:ext cx="1375920" cy="374760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1138,7 +1166,9 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
+      <c r="A13" s="8" t="n">
+        <v>7</v>
+      </c>
       <c r="B13" s="9" t="s">
         <v>28</v>
       </c>
@@ -1165,7 +1195,9 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8"/>
+      <c r="A14" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="B14" s="9" t="s">
         <v>31</v>
       </c>
@@ -1192,7 +1224,9 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8"/>
+      <c r="A15" s="8" t="n">
+        <v>9</v>
+      </c>
       <c r="B15" s="9" t="s">
         <v>33</v>
       </c>
@@ -1200,13 +1234,13 @@
         <v>1</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>13</v>
@@ -1214,26 +1248,26 @@
       <c r="H15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="I15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8"/>
+      <c r="A16" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="B16" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>11</v>
+      <c r="D16" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>13</v>
@@ -1241,26 +1275,26 @@
       <c r="H16" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="I16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
+      <c r="A17" s="8" t="n">
+        <v>11</v>
+      </c>
       <c r="B17" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>11</v>
+      <c r="D17" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>13</v>
@@ -1268,26 +1302,26 @@
       <c r="H17" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8"/>
+      <c r="A18" s="8" t="n">
+        <v>12</v>
+      </c>
       <c r="B18" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>11</v>
+      <c r="D18" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>13</v>
@@ -1295,14 +1329,14 @@
       <c r="H18" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="I18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8"/>
+      <c r="A19" s="8" t="n">
+        <v>13</v>
+      </c>
       <c r="B19" s="9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>3</v>
@@ -1314,7 +1348,7 @@
         <v>11</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>20</v>
@@ -1327,9 +1361,11 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8"/>
+      <c r="A20" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="B20" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>1</v>
@@ -1341,7 +1377,7 @@
         <v>11</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>13</v>
@@ -1354,9 +1390,11 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8"/>
+      <c r="A21" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="B21" s="9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>4</v>
@@ -1368,7 +1406,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>20</v>
@@ -1381,9 +1419,11 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8"/>
+      <c r="A22" s="8" t="n">
+        <v>16</v>
+      </c>
       <c r="B22" s="9" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>1</v>
@@ -1395,7 +1435,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>13</v>
@@ -1408,24 +1448,26 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8"/>
+      <c r="A23" s="8" t="n">
+        <v>17</v>
+      </c>
       <c r="B23" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>14</v>
@@ -1433,24 +1475,26 @@
       <c r="I23" s="18"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8"/>
+      <c r="A24" s="8" t="n">
+        <v>18</v>
+      </c>
       <c r="B24" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>14</v>
@@ -1458,24 +1502,26 @@
       <c r="I24" s="18"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8"/>
+      <c r="A25" s="8" t="n">
+        <v>19</v>
+      </c>
       <c r="B25" s="9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>14</v>
@@ -1483,24 +1529,26 @@
       <c r="I25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8"/>
+      <c r="A26" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="B26" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>69</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>71</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>14</v>
@@ -1508,68 +1556,96 @@
       <c r="I26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8"/>
+      <c r="A27" s="8" t="n">
+        <v>21</v>
+      </c>
       <c r="B27" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>14</v>
       </c>
       <c r="I27" s="12"/>
     </row>
-    <row r="30" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22"/>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="12"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="s">
+        <v>81</v>
+      </c>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
-      <c r="G31" s="23"/>
+      <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="I31" s="22"/>
     </row>
-    <row r="32" s="25" customFormat="true" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-    </row>
-    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+    </row>
+    <row r="33" s="25" customFormat="true" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+    </row>
     <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1607,12 +1683,12 @@
   <mergeCells count="4">
     <mergeCell ref="A2:B3"/>
     <mergeCell ref="D2:F4"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A33:I33"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A30" r:id="rId1" display="Need a quick and accurante quote? Need an efficient production? Please read SMT Ordering Necessary Files &amp; Info in 1 minute. Thank you very much!"/>
-    <hyperlink ref="A32" r:id="rId2" display="Click for Instructions on How to Create a BOM"/>
+    <hyperlink ref="A31" r:id="rId1" display="Need a quick and accurante quote? Need an efficient production? Please read SMT Ordering Necessary Files &amp; Info in 1 minute. Thank you very much!"/>
+    <hyperlink ref="A33" r:id="rId2" display="Click for Instructions on How to Create a BOM"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
